--- a/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N5_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N5_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>24.01585960716388</v>
+        <v>3.902577186164131</v>
       </c>
       <c r="D2" t="n">
-        <v>24.24334622632536</v>
+        <v>3.939543761777871</v>
       </c>
       <c r="E2" t="n">
-        <v>16.49360484379253</v>
+        <v>2.680210787116286</v>
       </c>
       <c r="F2" t="n">
-        <v>30.69470068635247</v>
+        <v>4.987888861532277</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>15.41097067184317</v>
+        <v>2.504282734174515</v>
       </c>
       <c r="D3" t="n">
-        <v>6.332631348630612</v>
+        <v>1.029052594152474</v>
       </c>
       <c r="E3" t="n">
-        <v>16.49360484379253</v>
+        <v>2.680210787116286</v>
       </c>
       <c r="F3" t="n">
-        <v>30.69470068635247</v>
+        <v>4.987888861532277</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>9.294764247276838</v>
+        <v>1.510399190182486</v>
       </c>
       <c r="D4" t="n">
-        <v>2.490144974788593</v>
+        <v>0.4046485584031463</v>
       </c>
       <c r="E4" t="n">
-        <v>16.49360484379253</v>
+        <v>2.680210787116286</v>
       </c>
       <c r="F4" t="n">
-        <v>30.69470068635247</v>
+        <v>4.987888861532277</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>52.49238963693302</v>
+        <v>8.530013316001616</v>
       </c>
       <c r="D5" t="n">
-        <v>51.39512583467762</v>
+        <v>8.351707948135115</v>
       </c>
       <c r="E5" t="n">
-        <v>16.49360484379253</v>
+        <v>2.680210787116286</v>
       </c>
       <c r="F5" t="n">
-        <v>30.69470068635247</v>
+        <v>4.987888861532277</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>48.80205348085546</v>
+        <v>7.930333690639012</v>
       </c>
       <c r="D6" t="n">
-        <v>13.02294700787581</v>
+        <v>2.116228888779819</v>
       </c>
       <c r="E6" t="n">
-        <v>16.49360484379253</v>
+        <v>2.680210787116286</v>
       </c>
       <c r="F6" t="n">
-        <v>30.69470068635247</v>
+        <v>4.987888861532277</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>40.70569781858524</v>
+        <v>6.614675895520103</v>
       </c>
       <c r="D7" t="n">
-        <v>89.71241500201475</v>
+        <v>14.5782674378274</v>
       </c>
       <c r="E7" t="n">
-        <v>16.49360484379253</v>
+        <v>2.680210787116286</v>
       </c>
       <c r="F7" t="n">
-        <v>30.69470068635247</v>
+        <v>4.987888861532277</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
